--- a/docs/research/provinces/SportsHub-Newfoundland-Labrador.xlsx
+++ b/docs/research/provinces/SportsHub-Newfoundland-Labrador.xlsx
@@ -11,12 +11,14 @@
     <sheet name="Leagues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Club-League Map" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Contacts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Club Sizes'!$A$1:$C$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -557,7 +559,6 @@
           <t>Bay Roberts / Conception Bay North area</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>709-738-3177</t>
@@ -608,7 +609,6 @@
           <t>https://rocksports.ca/basketball/conception-bay-north-minor-basketball/</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,27 +631,21 @@
           <t>Central NL (town unconfirmed)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>centralwolves@hotmail.com</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>U16 club team (Facebook group for U16 Club Team per NLBA registry)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>community club team</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>primary</t>
@@ -689,27 +683,21 @@
           <t>Central Newfoundland (town not published)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>centralwolves@hotmail.com</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>U16 club team (per Facebook page 'Central Wolves - U16 Club Team')</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>community club team</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>uncertain</t>
@@ -747,9 +735,6 @@
           <t>Conception Bay Centre (Holyrood/Avondale area communities)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>https://www.cbseeds.ca</t>
@@ -765,7 +750,6 @@
           <t>Youth basketball ages 5–16 in fun group settings; broader after-school youth programs (education + sports)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>community nonprofit (incorporated youth-initiatives org, volunteer-run)</t>
@@ -813,13 +797,6 @@
           <t>Conception Bay North (town unconfirmed — Bay Roberts/Carbonear area)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>community program</t>
@@ -867,27 +844,21 @@
           <t>Corner Brook</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/CornerBrookMinorBasketball/</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Youth minor basketball emphasizing 'FUNdamentals' - passing, shooting, ball handling, defense</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>primary</t>
@@ -930,7 +901,6 @@
           <t>Grenfell Campus, Memorial University, Corner Brook; summer league sessions at Corner Brook Civic Centre</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>bmarsden@mun.ca</t>
@@ -1008,7 +978,6 @@
           <t>Grenfell Campus, Memorial University, Corner Brook, NL (games at Corner Brook Civic Centre)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>bmarsden@mun.ca</t>
@@ -1081,8 +1050,6 @@
           <t>Corner Brook / Humber Valley region</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>wabcavalanche@gmail.com</t>
@@ -1093,19 +1060,16 @@
           <t>https://www.facebook.com/profile.php?id=61565000000000</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Travel/rep teams; inaugural U14 Boys team for 2025–26; camps and tryouts planned</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>community rep/travel club (new)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1143,13 +1107,6 @@
           <t>Fogo Island</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>school-based community program (uncertain)</t>
@@ -1212,7 +1169,6 @@
           <t>forcebasketballnl@gmail.com</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Jimmie Mullett</t>
@@ -1223,13 +1179,11 @@
           <t>Grades 4–8; 5–8 week skills sessions</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>community program</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>primary</t>
@@ -1267,8 +1221,6 @@
           <t>Gander</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
@@ -1371,7 +1323,6 @@
           <t>Pre-K to Grade 6 development club; skill development and team play; serves Goulds, Southern Shore and Bay Bulls</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>community club program operated by private brand (709 Basketball)</t>
@@ -1424,7 +1375,6 @@
           <t>Sessions at Goulds Elementary; Southern Shore programs at Bay Bulls Regional Lifestyle Centre</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>info@709basketball.com</t>
@@ -1435,7 +1385,6 @@
           <t>https://www.shorebasketballnl.com/</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Pre-K–Grade 8 per NLBA registry (709 site says Pre-K–Gr 6 core); skill development, house programming and club teams</t>
@@ -1493,21 +1442,16 @@
           <t>Grand Falls-Windsor</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>https://central-athletics.square.site</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>Children's sports programming; Girls Basketball League registration advertised</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>private children's sports business</t>
@@ -1555,7 +1499,6 @@
           <t>Grand Falls-Windsor</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>709-486-3136</t>
@@ -1566,7 +1509,6 @@
           <t>bcookegfw@hotmail.com</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Brian Cooke — listed contact/organizer (NLBA registry)</t>
@@ -1629,11 +1571,6 @@
           <t>Grand Falls-Windsor (central NL — town unconfirmed)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Girls/female club basketball (at least U12 team fielded)</t>
@@ -1691,13 +1628,6 @@
           <t>Labrador City</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>community program</t>
@@ -1750,7 +1680,6 @@
           <t>P.O. Box 39 RPO Centennial Square, Mount Pearl, NL A1N 2C1</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>mp.minor.bb@gmail.com</t>
@@ -1828,7 +1757,6 @@
           <t>Programs at All Hallows Elementary, North River</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Aspire.Rec@outlook.com</t>
@@ -1901,8 +1829,6 @@
           <t>Outer Cove</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>admin@709basketball.com</t>
@@ -2057,7 +1983,6 @@
           <t>Paradise</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>709-730-2763</t>
@@ -2386,20 +2311,16 @@
           <t>55 Hebron Way, St. John's, NL</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>https://www.raincitynl.com</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Youth team-sport development academy — extra coaching/team experience outside regular club or school play; basketball confirmed via NLBA minor-club membership</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
           <t>private academy (youth sports academy)</t>
@@ -2452,7 +2373,6 @@
           <t>Rock Sports Group Inc.: 145 Aberdeen Square, Unit 103, St. John's, NL</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
@@ -2473,7 +2393,6 @@
           <t>Invite-only/tryout-based elite program targeting the most dedicated players; sits atop Rock Sports community programs; related 'Future Hawks' youth boys fundamentals program</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>private academy (elite arm of Rock Sports Group Inc.)</t>
@@ -2685,8 +2604,6 @@
           <t>Torbay</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
@@ -2732,7 +2649,6 @@
           <t>https://rocksports.ca/basketball/</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2755,13 +2671,6 @@
           <t>Unknown (Newfoundland &amp; Labrador)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>community club (unconfirmed)</t>
@@ -2809,8 +2718,6 @@
           <t>Western Newfoundland (Corner Brook region; town not published)</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>wabcavalanche@gmail.com</t>
@@ -2821,19 +2728,16 @@
           <t>https://www.facebook.com/profile.php?id=61576765710305</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Youth club basketball for western Newfoundland (new club; details not yet published)</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>primary</t>
@@ -3096,7 +3000,6 @@
           <t>8 qualifying regions: Avalon, Central, Eastern, Labrador, Mount Pearl, South, St. John's North, Western</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>Qualifiers in season preceding each NL Games edition</t>
@@ -3154,8 +3057,6 @@
           <t>St. John's</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>League Standings and League Statistics pages hosted on northpointsports.com; registration via on-site web forms (no third-party registration platform identified)</t>
@@ -3208,7 +3109,6 @@
           <t>Corner Brook / Western Newfoundland</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Summer (July-August); 2026 youth summer program registration opened April 27, 2026</t>
@@ -4269,14 +4169,11 @@
           <t>Central NL (town unconfirmed)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>centralwolves@hotmail.com</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4289,14 +4186,11 @@
           <t>Central Newfoundland (town not published)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>centralwolves@hotmail.com</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4309,8 +4203,6 @@
           <t>Conception Bay Centre (Holyrood/Avondale area communities)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Jon (surname not published on accessible sources) — co-founder (fall 2020), communications &amp; fundraising, Coach &amp; Director of basketball programs; team incl. Krista Rebello</t>
@@ -4333,7 +4225,6 @@
           <t>Corner Brook</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>bmarsden@mun.ca</t>
@@ -4361,7 +4252,6 @@
           <t>Corner Brook</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>bmarsden@mun.ca</t>
@@ -4389,13 +4279,11 @@
           <t>Corner Brook / Humber Valley region</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>wabcavalanche@gmail.com</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>https://www.facebook.com/profile.php?id=61565000000000</t>
@@ -4428,7 +4316,6 @@
           <t>Jimmie Mullett</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4441,7 +4328,6 @@
           <t>Gander</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
@@ -4501,13 +4387,11 @@
           <t>Goulds (St. John's)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>info@709basketball.com</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>https://www.shorebasketballnl.com/</t>
@@ -4540,7 +4424,6 @@
           <t>Brian Cooke — listed contact/organizer (NLBA registry)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4553,7 +4436,6 @@
           <t>Mount Pearl</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>mp.minor.bb@gmail.com</t>
@@ -4581,7 +4463,6 @@
           <t>North River</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>Aspire.Rec@outlook.com</t>
@@ -4609,7 +4490,6 @@
           <t>Outer Cove</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>admin@709basketball.com</t>
@@ -4797,7 +4677,6 @@
           <t>St. John's</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
@@ -4889,7 +4768,6 @@
           <t>Torbay</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
@@ -4917,13 +4795,11 @@
           <t>Western Newfoundland (Corner Brook region; town not published)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>wabcavalanche@gmail.com</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>https://www.facebook.com/profile.php?id=61576765710305</t>
@@ -4934,4 +4810,236 @@
   <autoFilter ref="A1:F26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Teams counted (directional)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Breakdown (league=teams)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CE23 Academy</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=28; NLBA Minor Club Provincial Basketball =5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>St. John's Minor Basketball</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=20; NLBA Minor Club Provincial Basketball =2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Next Level Basketball Training</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=16; NLBA Minor Club Provincial Basketball =4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Avalon Basketball</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=14; NLBA Minor Club Provincial Basketball =2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mount Pearl Minor Basketball</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=4; NLBA Minor Club Provincial Basketball =1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Paradise Minor Basketball</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=4; NLBA Minor Club Provincial Basketball =1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Central NL Youth Basketball</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=4; NLBA Minor Club Provincial Basketball =1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>River Ratz</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Western</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Central Female Basketball</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=1; NLBA Minor Club Provincial Basketball =1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Burin</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CCB</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Grenfell Warriors</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NLBA Minor Club League=1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/research/provinces/SportsHub-Newfoundland-Labrador.xlsx
+++ b/docs/research/provinces/SportsHub-Newfoundland-Labrador.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Club Sizes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Clubs'!$A$1:$Q$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leagues'!$A$1:$L$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Club-League Map'!$A$1:$E$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Contacts'!$A$1:$F$26</definedName>
@@ -65,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -454,6 +455,7 @@
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,6 +539,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1549,6 +1556,9 @@
           <t>Appears as 'Central NL Minor' on the NLBA membership portal list. Grand Falls-Windsor also hosts the adult Donnini's senior league (excluded, adult-only). | Also listed as: Central NL Youth Basketball</t>
         </is>
       </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1606,6 +1616,9 @@
           <t>No website/social found; home town within central NL unconfirmed. Possibly connected to 'Central Athletics' (children's sports business in Grand Falls-Windsor running girls basketball league registration) — unverified, listed separately.</t>
         </is>
       </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1730,6 +1743,9 @@
           <t>Only major metro club NOT run by Rock Sports or 709 Basketball - classic volunteer nonprofit; multi-platform software sprawl (GOALLINE + RAMP + SportsEngine listing) = strong consolidation prospect.</t>
         </is>
       </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2038,6 +2054,9 @@
           <t>Canada Basketball Verified. Rock Sports Academy partnership per NLBA registry. Ryan Harnett: ryan@rocksports.ca / 709-640-9153.</t>
         </is>
       </c>
+      <c r="Q24" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2120,6 +2139,9 @@
           <t>709 Basketball is the umbrella brand (area code 709) covering Avalon, Outer Cove and Southern Shore Goulds; leadership names not published on site. Coaches NCCP/SafeSport trained. Two-week free trial offered. | Also listed as: Avalon Basketball (Avalon Basketball Association)</t>
         </is>
       </c>
+      <c r="Q25" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2284,6 +2306,9 @@
           <t>Fields many teams per division (at least 4 numbered U12 girls teams). Merch store on site.</t>
         </is>
       </c>
+      <c r="Q27" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2582,6 +2607,9 @@
           <t>Rock Sports Group Inc. also operates Paradise Minor Basketball, Gander Minor Basketball, St. John's Minor Football and Dennis Squires Academy. Canada Basketball Verified. Ryan Harnett: ryan@rocksports.ca / 709-640-9153.</t>
         </is>
       </c>
+      <c r="Q31" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2755,7 +2783,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P34"/>
+  <autoFilter ref="A1:Q34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/research/provinces/SportsHub-Newfoundland-Labrador.xlsx
+++ b/docs/research/provinces/SportsHub-Newfoundland-Labrador.xlsx
@@ -441,7 +441,7 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -471,77 +471,77 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Teams Counted</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Owner/Principal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Programs</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Leagues</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>Teams Counted</t>
         </is>
       </c>
     </row>
@@ -556,62 +556,62 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Avalon - Conception Bay North</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Bay Roberts / Conception Bay North area</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>709-738-3177</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>jamie@rocksports.ca</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>https://cbnminorbasketball.ca</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Operated by Rock Sports Academy Inc.; 'Jamie' (jamie@rocksports.ca) manages the CBN program</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Kindergarten-Grade 9; fundamentals-focused rec + club programming</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Rock Sports Group community minor basketball programs (house-league rec divisions)</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>community minor program operated by private company (Rock Sports Group Inc.)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Citrus Camps reported (Rock Sports standard)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://rocksports.ca/basketball/conception-bay-north-minor-basketball/</t>
         </is>
@@ -628,42 +628,42 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Central NL</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Central NL (town unconfirmed)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>centralwolves@hotmail.com</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>U16 club team (Facebook group for U16 Club Team per NLBA registry)</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>community club team</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/minor-clubs</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Listed on the NLBA minor-clubs registry with email + Facebook group only; no other web presence found. Not on the NLBA RAMP membership portal list at census time.</t>
         </is>
@@ -680,42 +680,42 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Central Newfoundland</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Central Newfoundland (town not published)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>centralwolves@hotmail.com</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>U16 club team (per Facebook page 'Central Wolves - U16 Club Team')</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>community club team</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/minor-clubs</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Listed on the NLBA minor-clubs registry with email + Facebook only; existence solid, everything else sparse.</t>
         </is>
@@ -732,52 +732,52 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Avalon (Conception Bay Centre)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Conception Bay Centre (Holyrood/Avondale area communities)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>https://www.cbseeds.ca</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Jon (surname not published on accessible sources) — co-founder (fall 2020), communications &amp; fundraising, Coach &amp; Director of basketball programs; team incl. Krista Rebello</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Youth basketball ages 5–16 in fun group settings; broader after-school youth programs (education + sports)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>community nonprofit (incorporated youth-initiatives org, volunteer-run)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>RAMP (CBSeeds.rampregistrations.com) for NLBA membership; site hosted on Google Sites</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://www.cbseeds.ca/</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Serves 'Conception Bay Centre' — NOT the Town of Conception Bay South; CBS town itself has no dedicated club found (metro clubs like Paradise/Mount Pearl/NLBT draw CBS players). cbseeds.ca did not resolve during census; details from indexed site content.</t>
         </is>
@@ -794,37 +794,37 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Conception Bay North</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Conception Bay North (town unconfirmed — Bay Roberts/Carbonear area)</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>community program</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>RAMP (CBNYouthBall.rampregistrations.com) for NLBA membership</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/membership</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Exists as an NLBA minor-club RAMP registration portal; no other web footprint found. Distinct from River Ratz (also CBN).</t>
         </is>
@@ -841,42 +841,42 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Western Newfoundland</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Corner Brook</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/CornerBrookMinorBasketball/</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Youth minor basketball emphasizing 'FUNdamentals' - passing, shooting, ball handling, defense</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://www.facebook.com/CornerBrookMinorBasketball/</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Facebook-only presence (handle: CornerBrookMinorBasketball); the only dedicated youth basketball club found in Corner Brook.</t>
         </is>
@@ -893,67 +893,67 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Western NL</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Corner Brook</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Grenfell Campus, Memorial University, Corner Brook; summer league sessions at Corner Brook Civic Centre</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>bmarsden@mun.ca</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>https://mun.ca/grenfellcampus/student-life/athletics--recreation/grenfell-warriors-youth-camps----summer-programs/</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Grenfell Campus Athletics &amp; Recreation (program contact: bmarsden@mun.ca)</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Junior Warriors Basketball (and Volleyball) youth programs; Grenfell Warriors Basketball Summer League with U12/U13/U14/U16 boys' and girls' divisions, 10-session blocks</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Grenfell Warriors Basketball Summer League; NLBA (minor club member)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>university athletics youth program (multi-sport org)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>JotForm (program registration), Eventbrite (summer league tickets), RAMP (GreenfellJRWarriors.rampregistrations.com) for NLBA membership</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/membership</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>The main organized youth basketball provider in Corner Brook. 2026 youth-program registration opens April 27, 2026.</t>
         </is>
@@ -970,67 +970,67 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Western Newfoundland</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Corner Brook</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Grenfell Campus, Memorial University, Corner Brook, NL (games at Corner Brook Civic Centre)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>bmarsden@mun.ca</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>https://mun.ca/grenfellcampus/student-life/athletics--recreation/grenfell-warriors-youth-camps----summer-programs/</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Grenfell Campus Athletics &amp; Recreation (Memorial University); B. Marsden - program contact</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Junior Warriors youth basketball + volleyball; Grenfell Warriors Basketball Summer League with U12 B/G, U13, U14 B/G, U16 divisions (10 sessions, skills + games)</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Grenfell Warriors Basketball Summer League</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>university athletics youth program (multi-sport org)</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Eventbrite (league registrations)</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>https://mun.ca/grenfellcampus/student-life/athletics--recreation/grenfell-warriors-youth-camps----summer-programs/</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Program operator rather than a member club, but it is the main organized youth basketball supply in Corner Brook alongside the Shooting Stars. Excluded from this census as clubs: SJABA/sjbball.ca (adult amateur league on TeamLinkt), Filipino Basketball Association NL (adult community league), school/varsity ball. No dedicated youth basketball club found for Conception Bay South, Labrador City, Happy Valley-Goose Bay, Stephenville or Clarenville despite targeted searches (July 2026).</t>
         </is>
@@ -1047,47 +1047,47 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Western NL (Humber Valley, Corner Brook–Deer Lake corridor)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Corner Brook / Humber Valley region</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>wabcavalanche@gmail.com</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>https://www.facebook.com/profile.php?id=61565000000000</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Travel/rep teams; inaugural U14 Boys team for 2025–26; camps and tryouts planned</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>community rep/travel club (new)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/minor-clubs</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>New club per NLBA registry (Facebook: Western Avalanche Basketball Club). No standalone website found; Facebook URL above is the page named on the registry — verify handle before outreach (search 'Western Avalanche Basketball Club' on Facebook).</t>
         </is>
@@ -1104,37 +1104,37 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Central NL / Notre Dame Bay</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Fogo Island</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>school-based community program (uncertain)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>RAMP (fogoislandcentralacademy.rampregistrations.com) for NLBA membership</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/membership</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Fogo Island Central Academy is a K-12 school, but it is listed under NLBA MINOR CLUB membership (NLBA maintains a separate 'School Team Membership' category), suggesting a community minor-basketball program run out of the school rather than a varsity team. Flagged for the school-exclusion rule — verify before counting.</t>
         </is>
@@ -1151,57 +1151,57 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Central NL</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Gander</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Operates from Gander Elementary</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>709-738-3177</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>forcebasketballnl@gmail.com</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Jimmie Mullett</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Grades 4–8; 5–8 week skills sessions</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>community program</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/minor-clubs</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>PSO registry entry (Facebook: FORCE Basketball NL). Coexists in Gander with Rock Sports Group's Gander Minor Basketball. Not on NLBA RAMP membership portal list at census time. | enriched 2026-07-18</t>
         </is>
@@ -1218,62 +1218,62 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Central Newfoundland</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Gander</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>https://ganderminorbasketball.ca</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Operated by Rock Sports Group Inc.</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Kindergarten-Grade 9 fundamentals + rec divisions</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Rock Sports Group community minor basketball programs (house-league rec divisions)</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>community minor program operated by private company (Rock Sports Group Inc.)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Citrus Camps reported (Rock Sports standard)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>https://rocksports.ca/basketball/</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>ganderminorbasketball.ca had SSL errors during research; Rock Sports page is the working source.</t>
         </is>
@@ -1290,67 +1290,67 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Avalon - Southern Shore &amp; Bay Bulls</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Goulds (St. John's)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>709 Basketball: 574 Topsail Road, St. John's, NL A1E 2C9</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>709-689-5332 (709 Basketball)</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>info@709basketball.com</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>gouldsbasketball.ca (registry-listed; not resolving July 2026)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Operated under 709 Basketball (same brand as Avalon Basketball); local principal not published</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Pre-K to Grade 6 development club; skill development and team play; serves Goulds, Southern Shore and Bay Bulls</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>community club program operated by private brand (709 Basketball)</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>TeamLinkt (app.teamlinkt.com/register/find/gouldsbasketball) + Citrus Camps (2024 via 709 Basketball)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/minor-clubs</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>Former standalone association now folded into 709 Basketball; websites shorebasketballnl.com and gouldsbasketball.ca both dead (DNS).</t>
         </is>
@@ -1367,62 +1367,62 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Avalon (Goulds / Southern Shore)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Goulds (St. John's)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Sessions at Goulds Elementary; Southern Shore programs at Bay Bulls Regional Lifestyle Centre</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>info@709basketball.com</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>https://www.shorebasketballnl.com/</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Pre-K–Grade 8 per NLBA registry (709 site says Pre-K–Gr 6 core); skill development, house programming and club teams</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>NLBA Minor Club League</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>community club program operated under 709 Basketball / Avalon Basketball umbrella</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>TeamLinkt (app.teamlinkt.com/register/find/gouldsbasketball), Citrus Camps, RAMP (SouthernShoreBasketball.rampregistrations.com)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/minor-clubs</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Listed as 'Goulds Basketball' on NLBA registry (site gouldsbasketball.ca, currently unresolvable) and as 'Southern Shore Goulds' on NLBA membership page; shorebasketballnl.com brands it Southern Shore Basketball Association.</t>
         </is>
@@ -1439,47 +1439,47 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Central NL</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Grand Falls-Windsor</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>https://central-athletics.square.site</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Children's sports programming; Girls Basketball League registration advertised</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>private children's sports business</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Square (square.site storefront/registration)</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>https://www.facebook.com/people/Central-Athletics/61565938269237/</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Facebook describes it as a 'sports based business for children' in Grand Falls-Windsor with girls basketball league registration open. Possible overlap/identity with the NLBA-registered 'Central Female Basketball' — unverified; kept as separate entry to avoid losing the lead.</t>
         </is>
@@ -1496,68 +1496,68 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Central NL</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Grand Falls-Windsor</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>709-486-3136</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>bcookegfw@hotmail.com</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Brian Cooke — listed contact/organizer (NLBA registry)</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Grades K–10; 10–14 week skills programs; club teams for provincial competition</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>NLBA Minor Club League; NLBA Minor Club Provincial Basketball Championships</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>community program/nonprofit</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>RAMP (CentralNLMinorBasketball.rampregistrations.com) for NLBA membership</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/minor-clubs</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Appears as 'Central NL Minor' on the NLBA membership portal list. Grand Falls-Windsor also hosts the adult Donnini's senior league (excluded, adult-only). | Also listed as: Central NL Youth Basketball</t>
         </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1571,53 +1571,53 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Central NL</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Grand Falls-Windsor (central NL — town unconfirmed)</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Girls/female club basketball (at least U12 team fielded)</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>NLBA Minor Club League; NLBA Minor Club Provincial Basketball Championships</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>community club (girls-focused)</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>RAMP (CentralFemaleBasketball.rampregistrations.com) for NLBA membership</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/membership</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>No website/social found; home town within central NL unconfirmed. Possibly connected to 'Central Athletics' (children's sports business in Grand Falls-Windsor running girls basketball league registration) — unverified, listed separately.</t>
         </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1631,37 +1631,37 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Labrador West (Labrador City/Wabush)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Labrador City</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>community program</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>RAMP (LWMB.rampregistrations.com) for NLBA membership</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/membership</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Named on the NLBA membership portal list ('Miner' spelling — mining-town identity); no other web footprint found. A 'Labrador Basketball League' Facebook group also exists for the region (https://www.facebook.com/groups/labradorbasketballleague/). No dedicated club found for Happy Valley-Goose Bay (YMCA/school/rec programming only).</t>
         </is>
@@ -1678,73 +1678,73 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Avalon - St. John's metro</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Mount Pearl</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>P.O. Box 39 RPO Centennial Square, Mount Pearl, NL A1N 2C1</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>mp.minor.bb@gmail.com</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>http://mountpearlbasketball.com</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Bobby Winsor - MPMBA representative on Mount Pearl Sports Alliance Board of Directors (president not published)</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Formed 1997; K-Grade 9 boys &amp; girls, recreational focus; jrCeltics house program; rep teams U12-U16</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>NLBA Minor Club Provincial Basketball Championships; NLBA Minor Club League</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>community nonprofit</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>GOALLINE (Stack Sports) website platform + RAMP registrations (mpmba.rampregistrations.com); also listed on SportsEngine org directory</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/minor-clubs</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Only major metro club NOT run by Rock Sports or 709 Basketball - classic volunteer nonprofit; multi-platform software sprawl (GOALLINE + RAMP + SportsEngine listing) = strong consolidation prospect.</t>
         </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -1758,67 +1758,67 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Conception Bay North</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>North River</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Programs at All Hallows Elementary, North River</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Aspire.Rec@outlook.com</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>https://www.facebook.com/northriverrec/</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Run by Aspire Recreation (Facebook: aspirerecreation); individual principal not published</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Grades 1–6 core; Jr. NBA 12-week fall/winter blocks + 8-week outdoor summer; U10/U12 club-league teams; teen basketball (13–17)</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>NLBA Minor Club League; NLBA Minor Club Provincial Basketball Championships</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>community nonprofit (program of Aspire Recreation / North River Recreation, a not-for-profit serving North River &amp; surrounding CBN communities)</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>RAMP (RiverRatz.rampregistrations.com) for NLBA membership</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/minor-clubs</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Multi-activity recreation nonprofit whose basketball arm is the River Ratz. | Also listed as: River Ratz Basketball Association</t>
         </is>
@@ -1835,62 +1835,62 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Avalon (Outer Cove / Torbay / St. John's East End)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Outer Cove</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>admin@709basketball.com</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>https://avalonbasketball.com/709-programs/blog-post-title-three-7l8bn-4jgt7-zykn5</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Danny Loveless</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Fall club teams U10 (Gr 2–4), U12 (Gr 5–6), U14 (Gr 7–8), U16 (Gr 9–10), U18 (Gr 11–12), boys and girls divisions</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>NLBA Minor Club League</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>community club program operated by Avalon Basketball Association / 709 Basketball</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>RAMP (OuterCoveBasketball.rampregistrations.com); parent org uses TeamLinkt + Citrus Camps</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>https://avalonbasketball.com/709-programs/blog-post-title-three-7l8bn-4jgt7-zykn5</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Not a standalone legal entity — a regional program of Avalon/709 Basketball serving Outer Cove, East End and Torbay, but holds its own NLBA minor-club registration portal. | enriched 2026-07-18</t>
         </is>
@@ -1907,72 +1907,72 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Avalon (St. John's metro)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Paradise</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>1260 Kenmount Road, Paradise, NL</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>709-782-8400</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>team@ce23basketball.com</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>https://www.ce23basketball.com</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Carl English — owner/operator (NL-born former NBA (Indiana Pacers) and European pro player)</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Youth programs U9–U18 boys &amp; girls (ages 5–18), weekly programs, summer camps, private facility gym-time bookings; fields multiple club teams per division</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>NLBA Minor Club League; NLBA Minor Club Provincial Basketball Championships</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>private academy (own full facility)</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>RAMP (CE23Academy.rampregistrations.com) for NLBA membership</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>https://www.ce23basketball.com/staff</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>25+ coaching staff listed for 2025-26. One of the largest private basketball operations in the province; NLBA head office (1296A Kenmount Rd, Paradise) is nearby.</t>
         </is>
@@ -1989,73 +1989,73 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Avalon (St. John's metro)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Paradise</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>709-730-2763</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>https://paradiseminorbasketball.ca</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Ryan Harnett and Jon Pye — listed principals/contacts; operated by Rock Sports Group Inc.</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>K–2 intro, U10 (Gr 3-4), U12 (Gr 5-6), U14 (Gr 7-8), U16; house league plus competitive club teams; Sept–May club season with monthly payment plan</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>NLBA Minor Club League; NLBA Minor Club Provincial Basketball Championships; Rock Sports Group community minor basketball programs (house-league rec divisions)</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>community club operated by private multi-sport operator (Rock Sports Group Inc.)</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>RAMP (ParadiseMinorBasketball.rampregistrations.com) for NLBA membership</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>https://paradiseminorbasketball.ca/</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Canada Basketball Verified. Rock Sports Academy partnership per NLBA registry. Ryan Harnett: ryan@rocksports.ca / 709-640-9153.</t>
         </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -2069,78 +2069,78 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Avalon (St. John's metro, east end)</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>St. John's</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Programs at Northpoint Sports (425 Topsail Rd) and Paul Reynolds Community Centre; 709 Basketball umbrella address 574 Topsail Road, St. John's, NL A1E 2C9</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>709-689-5332</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>admin@709basketball.com</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>https://avalonbasketball.com</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Ethan Knight - lead coach/program head (2025 NLBA Minor Coach of the Year); ownership sits with 709 Basketball (owner not published)</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Junior Hoops (Pre-K–Gr 1), club basketball Gr 2–12 (U8/U10/U12/U14/U16/U18 boys &amp; girls), small-group and private training; ages 4–18</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>NLBA Minor Club League; NLBA Minor Club Provincial Basketball Championships; Avalon Basketball 3v3 League (internal)</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>club program under 709 Basketball umbrella (privately operated club brand; also runs Outer Cove and Southern Shore Goulds programs)</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>TeamLinkt (club registration), Citrus Camps (register.citruscamps.com club membership), RAMP (NLBA membership via 709Basketball.rampregistrations.com)</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/minor-clubs</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>709 Basketball is the umbrella brand (area code 709) covering Avalon, Outer Cove and Southern Shore Goulds; leadership names not published on site. Coaches NCCP/SafeSport trained. Two-week free trial offered. | Also listed as: Avalon Basketball (Avalon Basketball Association)</t>
         </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="26">
@@ -2154,72 +2154,72 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Avalon (St. John's)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>St. John's</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>42 O'Leary Avenue, St. John's, NL A1B 2C7</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>709-579-1541</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>info@northpointsports.ca</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>https://northpointsports.com/court-college</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>John Langdon and Chad Langdon — men's coaching staff and named contacts at Northpoint Sports (john@northpointsports.ca, chad@northpointsports.ca); Maria Carroll and Karoline Keating lead women's coaching</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>CCB Core Training 8-week progressive cycles for U12/U14/U16 ($225); CCB Selects invitation-only U16 team (Sept–May/June, trains 2x/week, off-island tournaments)</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Northpoint Sports Basketball League</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>private academy / training program inside private sports facility (FIBA-size court + pickleball courts)</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Website registration form; Cojilio (booking.cojilio.com/northpointsports) for facility bookings</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://northpointsports.com/court-college</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>NLBA registry also notes Avalon Basketball runs programs at a Northpoint Sports location (425 Topsail Rd listed there vs 42 O'Leary Ave on Northpoint's own site — possibly two sites or a move). Instagram @courtcollegebasketball / @ccb_selects.</t>
         </is>
@@ -2236,78 +2236,78 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Avalon (St. John's + Southern Shore/Bay Bulls)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>St. John's</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Multiple venues; Southern Shore programs at Bay Bulls Regional Lifestyle Centre</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>709-690-5255</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>info@nlbt.ca</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>https://www.nlbt.ca</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Scott Noftall — owner/operator (per club Facebook page); 'Angela' listed as phone contact on NLBA registry</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>K–U18: skills programs (Million Makes Scoring, Handles and Shooting/Scoring), club teams U10/U12/U14/U16 boys &amp; girls, travel teams, Easter and summer camps; Southern Shore satellite programming</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>NLBA Minor Club League; NLBA Minor Club Provincial Basketball Championships</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>private academy</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>RAMP (NextLevelBasketballTraining.rampregistrations.com) for NLBA membership</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>https://www.nlbt.ca/</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>Fields many teams per division (at least 4 numbered U12 girls teams). Merch store on site.</t>
         </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -2321,52 +2321,52 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Avalon (St. John's)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>St. John's</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>55 Hebron Way, St. John's, NL</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>https://www.raincitynl.com</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Youth team-sport development academy — extra coaching/team experience outside regular club or school play; basketball confirmed via NLBA minor-club membership</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>private academy (youth sports academy)</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>RAMP (RCA.rampregistrations.com) for NLBA membership; site on Google Sites (raincityathletics.info)</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>https://www.facebook.com/raincitynl/</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Founder names not published on accessible pages; raincitynl.com/about returned 404 and Google Sites domain requires login.</t>
         </is>
@@ -2383,62 +2383,62 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Avalon - St. John's metro</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>St. John's</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Rock Sports Group Inc.: 145 Aberdeen Square, Unit 103, St. John's, NL</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>https://www.rockelite.ca</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Jon Pye - Director of Operations, Rock Sports (staff page on rockelite.ca)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Invite-only/tryout-based elite program targeting the most dedicated players; sits atop Rock Sports community programs; related 'Future Hawks' youth boys fundamentals program</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>private academy (elite arm of Rock Sports Group Inc.)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Citrus Camps reported (Rock Sports standard)</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>https://rocksports.ca/basketball/</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>rockelite.ca DNS unresolvable from research environment but indexed pages confirm site and staff.</t>
         </is>
@@ -2455,72 +2455,72 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Avalon + island-wide</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>St. John's</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>145 Aberdeen Square, Unit 103, St. John's, NL</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>709-738-3177</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>https://rocksports.ca</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Jon Pye - Director of Operations; Ryan Harnett - staff (Master's in Global Sports Business)</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Private operator of community minor basketball across NL: St. John's Minor, Paradise Minor, Gander Minor, CBN Minor, Torbay Minor, Rock Elite, Future Hawks; house-league rec divisions + club teams + camps</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Rock Sports Group community minor basketball programs (house-league rec divisions); NLBA Minor Club League; NLBA Minor Club Provincial Basketball Championships</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>private multi-sport/multi-program operator</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Citrus Camps (register.citruscamps.com) across programs; WordPress sites per club</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>https://rocksports.ca/basketball/</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Highest-leverage GTM target in the province: one company runs 6+ community basketball brands on Citrus Camps.</t>
         </is>
@@ -2537,78 +2537,78 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="n">
+        <v>22</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — Avalon (St. John's East)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>St. John's</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Venues: Ches Penney YMCA, Paul Reynolds Community Centre, Memorial University</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>709-730-2763</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>https://www.sjmb.ca</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Jon Pye and Ryan Harnett — listed principals/contacts; operated by Rock Sports Group Inc.</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>K–U16: camps (summer, K-2 / Gr 3-4 etc.), skills sessions, house programming, competitive club teams U12/U14/U16 incl. High Performance stream</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>NLBA Minor Club League; NLBA Minor Club Provincial Basketball Championships; Rock Sports Group community minor basketball programs (house-league rec divisions)</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>community club operated by private multi-sport operator (Rock Sports Group Inc.)</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>RAMP (SJMBA.rampregistrations.com) for NLBA membership; registration via SJMB.ca</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>verified</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>https://sjmb.ca/</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Rock Sports Group Inc. also operates Paradise Minor Basketball, Gander Minor Basketball, St. John's Minor Football and Dennis Squires Academy. Canada Basketball Verified. Ryan Harnett: ryan@rocksports.ca / 709-640-9153.</t>
         </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -2622,57 +2622,57 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Avalon - northeast Avalon</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Torbay</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>jon@rocksports.ca</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>https://torbayminorbasketball.ca</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Operated by Rock Sports Academy Inc.</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Pre-Kindergarten to Grade 2 intro program</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Rock Sports Group community minor basketball programs (house-league rec divisions)</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>community minor program operated by private company (Rock Sports Group Inc.)</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Citrus Camps reported (Rock Sports standard)</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>https://rocksports.ca/basketball/</t>
         </is>
@@ -2689,37 +2689,37 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Newfoundland &amp; Labrador — location unconfirmed</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Unknown (Newfoundland &amp; Labrador)</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>community club (unconfirmed)</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>RAMP (riversideraptorsbasketball.rampregistrations.com) for NLBA membership</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/membership</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Appears only as an NLBA minor-club RAMP portal; no locatable web presence. 'Riverside' matches several NL communities/schools (e.g., Riverside Elementary, Shoal Harbour/Clarenville) — unverified.</t>
         </is>
@@ -2736,47 +2736,47 @@
           <t>Newfoundland &amp; Labrador</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Western Newfoundland</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Western Newfoundland (Corner Brook region; town not published)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>wabcavalanche@gmail.com</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>https://www.facebook.com/profile.php?id=61576765710305</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Youth club basketball for western Newfoundland (new club; details not yet published)</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>community club</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>https://www.newfoundlandlabradorbasketball.com/minor-clubs</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Newly listed on NLBA minor-clubs registry; Facebook page ID suggests created 2025.</t>
         </is>
